--- a/data/trans_dic/IP16B01-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP16B01-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos recetados por el médico para el catarro, gripe, garganta, bronquios</t>
+          <t>Menores que consumiero medicamentos recetados por el médico para el catarro, gripe, garganta, bronquios (tasa de respuesta: 99,34%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -614,7 +615,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -677,54 +678,54 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,64</t>
+          <t>0,0; 29,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>63,47; 95,87</t>
+          <t>62,46; 96,14</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20,79; 79,75</t>
+          <t>19,67; 79,66</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>74,89; 100,0</t>
+          <t>70,9; 100,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>50,47; 93,78</t>
+          <t>48,41; 92,68</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,87</t>
+          <t>0,0; 16,16</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>74,12; 97,11</t>
+          <t>74,16; 97,43</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>44,95; 82,52</t>
+          <t>46,18; 82,62</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -787,54 +788,54 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 6,81</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>62,68; 95,59</t>
+          <t>63,09; 95,5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>70,45; 96,79</t>
+          <t>71,43; 96,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 6,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>73,65; 100,0</t>
+          <t>74,89; 100,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>89,47; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0; 3,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>75,49; 93,76</t>
+          <t>75,67; 94,17</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>80,73; 97,91</t>
+          <t>79,93; 97,84</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -897,27 +898,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 11,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>88,17; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>76,75; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>79,36; 100,0</t>
+          <t>83,28; 100,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -927,17 +928,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 5,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>87,42; 100,0</t>
+          <t>87,52; 100,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>65,35; 100,0</t>
+          <t>62,66; 100,0</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 7,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>56,33; 91,52</t>
+          <t>53,94; 91,54</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>65,54; 100,0</t>
+          <t>63,76; 100,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0; 7,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>67,36; 100,0</t>
+          <t>66,62; 100,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,03; 95,05</t>
+          <t>60,33; 95,71</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0; 3,98</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>65,78; 92,09</t>
+          <t>67,39; 94,14</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>72,63; 94,87</t>
+          <t>73,51; 94,6</t>
         </is>
       </c>
     </row>
@@ -1117,54 +1118,54 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>57,53; 94,68</t>
+          <t>58,94; 94,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>79,25; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>54,34; 100,0</t>
+          <t>46,38; 100,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>69,43; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0; 7,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>64,12; 93,2</t>
+          <t>63,58; 93,01</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>86,51; 100</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1227,54 +1228,54 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 9,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>30,53; 92,28</t>
+          <t>31,09; 92,43</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>25,49; 88,21</t>
+          <t>19,67; 87,7</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>63,71; 100,0</t>
+          <t>70,43; 100,0</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19,63; 100,0</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 5,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>63,53; 95,63</t>
+          <t>62,38; 95,59</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>32,72; 90,61</t>
+          <t>28,01; 91,05</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1337,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0; 5,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>64,72; 95,79</t>
+          <t>64,76; 95,77</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>38,8; 86,69</t>
+          <t>37,55; 86,36</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0; 4,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>76,75; 100,0</t>
+          <t>76,72; 100,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,49; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0; 2,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>75,65; 95,67</t>
+          <t>77,75; 95,63</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>62,52; 92,53</t>
+          <t>62,12; 92,8</t>
         </is>
       </c>
     </row>
@@ -1447,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,22</t>
+          <t>0,0; 12,53</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>49,28; 94,24</t>
+          <t>52,03; 94,09</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>70,02; 100,0</t>
+          <t>63,86; 100,0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0; 3,04</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>89,47; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>66,69; 100,0</t>
+          <t>74,05; 100,0</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,92</t>
+          <t>0,0; 4,89</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>72,57; 97,27</t>
+          <t>70,56; 97,14</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>78,3; 100,0</t>
+          <t>76,48; 100,0</t>
         </is>
       </c>
     </row>
@@ -1557,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,51</t>
+          <t>0,0; 3,76</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>75,19; 88,06</t>
+          <t>75,35; 88,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>73,73; 88,63</t>
+          <t>73,88; 87,83</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 0,89</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>87,87; 96,99</t>
+          <t>88,05; 97,03</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>81,16; 93,98</t>
+          <t>80,09; 93,75</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,77</t>
+          <t>0,0; 1,87</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>83,68; 91,27</t>
+          <t>83,55; 91,28</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>80,18; 89,58</t>
+          <t>79,58; 89,15</t>
         </is>
       </c>
     </row>
@@ -1626,4 +1627,1611 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que consumiero medicamentos recetados por el médico para el catarro, gripe, garganta, bronquios (tasa de respuesta: 99,34%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>707</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>10917</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3988</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>9289</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>8779</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>707</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>20207</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>12767</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3385</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>8032; 12362</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1537; 6222</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>6992; 9861</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>5598; 10718</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3847</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>16850; 22135</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>8948; 16007</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>11384</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>17086</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>13781</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>10658</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>25165</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>27745</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>8765; 13267</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>14007; 18967</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>11245; 15016</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>21877; 27223</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>24193; 29614</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>10348</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>5020</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>17058</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>4062</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>27406</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>9082</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>14790; 17759</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1920; 4802</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>24600; 28107</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>6154; 9822</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>11950</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>11624</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>9391</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>12578</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>21340</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>24201</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>8373; 14209</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>8348; 13092</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>6785; 10184</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>9214; 14617</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>17324; 24200</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>20850; 26833</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>10057</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>5740</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>7854</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>3187</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>17911</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>8927</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>7204; 11544</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>4481; 9660</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>13914; 20353</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>4191</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>2926</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>9606</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>2191</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>13797</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>5117</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>1909; 5676</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>990; 4412</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>7287; 10346</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3167</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>10285; 15760</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>2297; 7464</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>13355</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>6274</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>13614</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>7947</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>26968</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>14221</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>10425; 15418</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>3582; 8238</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>10940; 14259</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>23602; 29031</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>10862; 16228</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>8672</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>9760</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>11862</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>9578</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>20534</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>19338</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>0; 3248</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>5787; 10464</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>6738; 10552</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>7542; 10185</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>0; 3217</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>16217; 22326</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>15859; 20737</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>1349</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>80874</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>62418</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>92453</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>58981</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>1349</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>173326</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>121399</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>0; 4707</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>73996; 86422</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>56439; 67099</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>87123; 96011</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>53488; 62610</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>0; 5026</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>164724; 179957</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>113939; 127644</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16B01-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP16B01-Provincia-trans_dic.xlsx
@@ -678,17 +678,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,01</t>
+          <t>0,0; 31,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>62,46; 96,14</t>
+          <t>63,34; 95,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19,67; 79,66</t>
+          <t>20,38; 80,89</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -698,27 +698,27 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>70,9; 100,0</t>
+          <t>69,61; 100,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>48,41; 92,68</t>
+          <t>49,22; 93,87</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,16</t>
+          <t>0,0; 13,83</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>74,16; 97,43</t>
+          <t>74,52; 97,34</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>46,18; 82,62</t>
+          <t>45,49; 82,23</t>
         </is>
       </c>
     </row>
@@ -793,12 +793,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>63,09; 95,5</t>
+          <t>59,52; 95,52</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>71,43; 96,72</t>
+          <t>70,33; 96,97</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>74,89; 100,0</t>
+          <t>71,07; 100,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -823,12 +823,12 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>75,67; 94,17</t>
+          <t>75,43; 95,66</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>79,93; 97,84</t>
+          <t>81,11; 97,83</t>
         </is>
       </c>
     </row>
@@ -918,12 +918,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>83,28; 100,0</t>
+          <t>79,72; 100,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>39,99; 100,0</t>
+          <t>40,23; 100,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -933,12 +933,12 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>87,52; 100,0</t>
+          <t>89,12; 100,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>62,66; 100,0</t>
+          <t>65,35; 100,0</t>
         </is>
       </c>
     </row>
@@ -1013,12 +1013,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>53,94; 91,54</t>
+          <t>54,1; 91,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>63,76; 100,0</t>
+          <t>66,5; 100,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>66,62; 100,0</t>
+          <t>66,63; 100,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>60,33; 95,71</t>
+          <t>62,57; 95,72</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>67,39; 94,14</t>
+          <t>66,29; 93,69</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>73,51; 94,6</t>
+          <t>72,09; 93,32</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>58,94; 94,44</t>
+          <t>56,92; 94,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>46,38; 100,0</t>
+          <t>46,31; 100,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>63,58; 93,01</t>
+          <t>64,19; 93,26</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>31,09; 92,43</t>
+          <t>31,16; 92,31</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>19,67; 87,7</t>
+          <t>19,4; 87,77</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1248,12 +1248,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>70,43; 100,0</t>
+          <t>69,55; 100,0</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 100,0</t>
+          <t>19,63; 100,0</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1263,12 +1263,12 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>62,38; 95,59</t>
+          <t>64,0; 95,59</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>28,01; 91,05</t>
+          <t>28,46; 90,89</t>
         </is>
       </c>
     </row>
@@ -1343,12 +1343,12 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>64,76; 95,77</t>
+          <t>62,16; 95,72</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>37,55; 86,36</t>
+          <t>40,62; 86,53</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>76,72; 100,0</t>
+          <t>76,21; 100,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1373,12 +1373,12 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>77,75; 95,63</t>
+          <t>75,56; 95,61</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>62,12; 92,8</t>
+          <t>62,49; 93,05</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,53</t>
+          <t>0,0; 15,41</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>52,03; 94,09</t>
+          <t>50,8; 94,0</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>63,86; 100,0</t>
+          <t>69,59; 100,0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1473,22 +1473,22 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>74,05; 100,0</t>
+          <t>66,94; 100,0</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,89</t>
+          <t>0,0; 4,46</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>70,56; 97,14</t>
+          <t>71,05; 97,18</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>76,48; 100,0</t>
+          <t>77,52; 100,0</t>
         </is>
       </c>
     </row>
@@ -1558,17 +1558,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,76</t>
+          <t>0,0; 3,77</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>75,35; 88,0</t>
+          <t>75,02; 87,8</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>73,88; 87,83</t>
+          <t>73,09; 87,76</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1578,27 +1578,27 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>88,05; 97,03</t>
+          <t>87,96; 96,77</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>80,09; 93,75</t>
+          <t>80,18; 93,61</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,87</t>
+          <t>0,0; 1,75</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>83,55; 91,28</t>
+          <t>83,82; 91,34</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>79,58; 89,15</t>
+          <t>79,46; 89,31</t>
         </is>
       </c>
     </row>
@@ -1861,17 +1861,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3385</t>
+          <t>0; 3638</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8032; 12362</t>
+          <t>8144; 12335</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1537; 6222</t>
+          <t>1592; 6318</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1881,27 +1881,27 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6992; 9861</t>
+          <t>6864; 9861</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5598; 10718</t>
+          <t>5692; 10855</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3847</t>
+          <t>0; 3291</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>16850; 22135</t>
+          <t>16932; 22116</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>8948; 16007</t>
+          <t>8814; 15932</t>
         </is>
       </c>
     </row>
@@ -2029,12 +2029,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8765; 13267</t>
+          <t>8269; 13271</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14007; 18967</t>
+          <t>13792; 19015</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>11245; 15016</t>
+          <t>10672; 15016</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -2059,12 +2059,12 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>21877; 27223</t>
+          <t>21806; 27655</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>24193; 29614</t>
+          <t>24551; 29611</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>14790; 17759</t>
+          <t>14157; 17759</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1920; 4802</t>
+          <t>1932; 4802</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>24600; 28107</t>
+          <t>25048; 28107</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6154; 9822</t>
+          <t>6419; 9822</t>
         </is>
       </c>
     </row>
@@ -2355,12 +2355,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8373; 14209</t>
+          <t>8398; 14230</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8348; 13092</t>
+          <t>8707; 13092</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9214; 14617</t>
+          <t>9557; 14619</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -2385,12 +2385,12 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>17324; 24200</t>
+          <t>17040; 24085</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>20850; 26833</t>
+          <t>20447; 26469</t>
         </is>
       </c>
     </row>
@@ -2518,7 +2518,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>7204; 11544</t>
+          <t>6957; 11527</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4481; 9660</t>
+          <t>4474; 9660</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>13914; 20353</t>
+          <t>14047; 20409</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1909; 5676</t>
+          <t>1914; 5669</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>990; 4412</t>
+          <t>976; 4416</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -2696,12 +2696,12 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>7287; 10346</t>
+          <t>7196; 10346</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 3167</t>
+          <t>622; 3167</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -2711,12 +2711,12 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>10285; 15760</t>
+          <t>10551; 15759</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2297; 7464</t>
+          <t>2334; 7451</t>
         </is>
       </c>
     </row>
@@ -2844,12 +2844,12 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>10425; 15418</t>
+          <t>10007; 15410</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3582; 8238</t>
+          <t>3874; 8254</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>10940; 14259</t>
+          <t>10866; 14259</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>23602; 29031</t>
+          <t>22937; 29025</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>10862; 16228</t>
+          <t>10927; 16270</t>
         </is>
       </c>
     </row>
@@ -3002,17 +3002,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 3248</t>
+          <t>0; 3996</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>5787; 10464</t>
+          <t>5649; 10454</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>6738; 10552</t>
+          <t>7343; 10552</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -3027,22 +3027,22 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>7542; 10185</t>
+          <t>6818; 10185</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0; 3217</t>
+          <t>0; 2936</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>16217; 22326</t>
+          <t>16330; 22335</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>15859; 20737</t>
+          <t>16075; 20737</t>
         </is>
       </c>
     </row>
@@ -3165,17 +3165,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>0; 4707</t>
+          <t>0; 4725</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>73996; 86422</t>
+          <t>73677; 86225</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>56439; 67099</t>
+          <t>55837; 67045</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -3185,27 +3185,27 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>87123; 96011</t>
+          <t>87037; 95751</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>53488; 62610</t>
+          <t>53546; 62516</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>0; 5026</t>
+          <t>0; 4704</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>164724; 179957</t>
+          <t>165258; 180086</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>113939; 127644</t>
+          <t>113767; 127868</t>
         </is>
       </c>
     </row>
